--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 71 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 70 clubs short</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4883,8 +4883,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -14296,7 +14296,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 70 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 68 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA136"/>
+  <dimension ref="A1:AA137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>1</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6047,8 +6047,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6414,8 +6414,8 @@
       <c r="R59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="9" t="n">
-        <v>0</v>
+      <c r="S59" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T59" s="10" t="n">
         <v>1</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8569,8 +8569,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -11265,7 +11265,7 @@
         <v>2</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -12953,15 +12953,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>946002</v>
+        <v>28680898</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad Toastmasters</t>
+          <t>General Datum Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13002,37 +13002,37 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q127" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28679268</v>
+        <v>946002</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Quantium India Toastmasters</t>
+          <t>Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,25 +13072,25 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O128" s="7" t="inlineStr">
@@ -13099,10 +13099,10 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13117,22 +13117,22 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="9" t="n">
-        <v>0</v>
+      <c r="X128" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA128" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -13147,11 +13147,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28678070</v>
+        <v>28679268</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Thryve Digital Hyderabad Toast Masters</t>
+          <t>Quantium India Toastmasters</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13169,10 +13169,10 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K129" s="4" t="n">
         <v>0</v>
@@ -13183,11 +13183,11 @@
         </is>
       </c>
       <c r="M129" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O129" s="7" t="inlineStr">
@@ -13220,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="X129" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13228,8 +13228,8 @@
       <c r="Z129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA129" s="10" t="n">
-        <v>1</v>
+      <c r="AA129" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>2694327</v>
+        <v>28678070</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters CBIT</t>
+          <t>Thryve Digital Hyderabad Toast Masters</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0</v>
@@ -13304,11 +13304,11 @@
       <c r="S130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U130" s="10" t="n">
-        <v>1</v>
+      <c r="T130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
         <v>0</v>
@@ -13316,8 +13316,8 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="10" t="n">
-        <v>7</v>
+      <c r="X130" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -13337,15 +13337,15 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28679838</v>
+        <v>2694327</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Amazon HYD Toastmasters Club</t>
+          <t>Toastmasters CBIT</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -13401,26 +13401,26 @@
       <c r="S131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" s="10" t="n">
-        <v>4</v>
+      <c r="T131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="10" t="n">
-        <v>1</v>
+      <c r="Z131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -13438,15 +13438,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28675603</v>
+        <v>28679838</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Avatar Toastmasters Club</t>
+          <t>Amazon HYD Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -13496,10 +13496,10 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T132" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
@@ -13508,10 +13508,10 @@
         <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1431155</v>
+        <v>28675603</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Broadridge Toastmasters Club</t>
+          <t>Avatar Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -13593,10 +13593,10 @@
         <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -13605,7 +13605,7 @@
         <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>7</v>
@@ -13632,15 +13632,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>2097754</v>
+        <v>1431155</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Oracle Hyderabad Toastmasters</t>
+          <t>Broadridge Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,17 +13654,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L134" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
@@ -13698,20 +13698,20 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>2</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>1</v>
+      <c r="X134" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -13729,11 +13729,11 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28677983</v>
+        <v>2097754</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>ValueMomentum-Hyderabad</t>
+          <t>Oracle Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -13765,11 +13765,11 @@
         </is>
       </c>
       <c r="M135" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O135" s="7" t="inlineStr">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -13796,13 +13796,13 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -13810,8 +13810,8 @@
       <c r="Z135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA135" s="9" t="n">
-        <v>0</v>
+      <c r="AA135" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -13826,93 +13826,190 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
+        <v>28677983</v>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>ValueMomentum-Hyderabad</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M136" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
         <v>28679192</v>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>Zelis Toastmasters Club</t>
         </is>
       </c>
-      <c r="E136" s="5" t="n">
+      <c r="E137" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F136" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G136" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
+      <c r="F137" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I136" s="4" t="n">
+      <c r="I137" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="J136" s="4" t="n">
+      <c r="J137" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
+      <c r="K137" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M136" s="8" t="n">
+      <c r="M137" s="8" t="n">
         <v>46446</v>
       </c>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="N137" s="4" t="inlineStr">
         <is>
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O136" s="7" t="inlineStr">
+      <c r="O137" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P136" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" s="10" t="n">
+      <c r="P137" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Y136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA136" s="10" t="n">
+      <c r="Q137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA136"/>
+  <autoFilter ref="A1:AA137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14395,7 +14492,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -14428,7 +14525,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14593,7 +14690,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14887,16 +14984,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -14905,7 +15002,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 68 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 43 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA137"/>
+  <dimension ref="A1:AA139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1167,8 +1167,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P5" s="9" t="n">
-        <v>3</v>
+      <c r="P5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q5" s="10" t="n">
         <v>2</v>
@@ -1176,8 +1176,8 @@
       <c r="R5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="9" t="n">
-        <v>1</v>
+      <c r="S5" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T5" s="9" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1294,8 +1294,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>1</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3428,8 +3428,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4010,8 +4010,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5145,22 +5145,22 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V46" s="9" t="n">
         <v>0</v>
@@ -5168,8 +5168,8 @@
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X46" s="9" t="n">
-        <v>3</v>
+      <c r="X46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5533,22 +5533,22 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="9" t="n">
-        <v>1</v>
+      <c r="S50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U50" s="9" t="n">
-        <v>0</v>
+      <c r="U50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V50" s="9" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5630,22 +5630,22 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q51" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
+      <c r="S51" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V51" s="9" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5824,25 +5824,25 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6629,8 +6629,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -6726,8 +6726,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6803,7 +6803,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>0</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -6842,15 +6842,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1530783</v>
+        <v>28680947</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Madhapur Toastmasters</t>
+          <t>Eastman Voices of Excellence</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,17 +6864,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T64" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U64" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V64" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -6939,15 +6939,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>28676243</v>
+        <v>1530783</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Providence India Toastmasters</t>
+          <t>Madhapur Toastmasters</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -6988,37 +6988,37 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="9" t="n">
-        <v>0</v>
+      <c r="S65" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7036,11 +7036,11 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>28676178</v>
+        <v>28676243</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Servicenow India Toastmasters Club</t>
+          <t>Providence India Toastmasters</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7094,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="9" t="n">
         <v>0</v>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7133,11 +7133,11 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1534632</v>
+        <v>28676178</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>TCS Maitree Synergy Park Toastmasters Club</t>
+          <t>Servicenow India Toastmasters Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
@@ -7200,13 +7200,13 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X67" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7226,19 +7226,19 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>28678821</v>
+        <v>1534632</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>BEN's Toastmasters Club</t>
+          <t>TCS Maitree Synergy Park Toastmasters Club</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>2</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
@@ -7296,14 +7296,14 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W68" s="10" t="n">
+      <c r="V68" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="X68" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -7327,15 +7327,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>28677306</v>
+        <v>28678821</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Pepsico Hyderabad Toastmasters Club</t>
+          <t>BEN's Toastmasters Club</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>0</v>
@@ -7396,11 +7396,11 @@
       <c r="V69" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W69" s="9" t="n">
-        <v>0</v>
+      <c r="W69" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X69" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
@@ -7424,15 +7424,15 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>28678121</v>
+        <v>28677306</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Salesforce Hyderabad Toastmasters</t>
+          <t>Pepsico Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -7490,14 +7490,14 @@
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>0</v>
+      <c r="V70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7521,11 +7521,11 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>991226</v>
+        <v>28678121</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Vision Toastmasters (Community Club)</t>
+          <t>Salesforce Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -7588,13 +7588,13 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -7618,15 +7618,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>28676685</v>
+        <v>991226</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>VNR VJIET Toastmasters Club</t>
+          <t>Vision Toastmasters (Community Club)</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -7670,13 +7670,13 @@
         <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="10" t="n">
-        <v>2</v>
+      <c r="S72" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -7684,11 +7684,11 @@
       <c r="U72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="10" t="n">
-        <v>4</v>
+      <c r="V72" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>7</v>
@@ -7706,24 +7706,24 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1272701</v>
+        <v>28676685</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Elan Toastmasters Hyderabad</t>
+          <t>VNR VJIET Toastmasters Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7737,17 +7737,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -7764,16 +7764,16 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="9" t="n">
-        <v>0</v>
+      <c r="S73" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -7781,11 +7781,11 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>2</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>7</v>
@@ -7793,8 +7793,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -7812,11 +7812,11 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>28676684</v>
+        <v>1272701</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Sattvic Toastmasters For Healthy Living</t>
+          <t>Elan Toastmasters Hyderabad</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -7879,13 +7879,13 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X74" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -7909,15 +7909,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>7913211</v>
+        <v>28676684</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Vijayawada Toastmasters Club</t>
+          <t>Sattvic Toastmasters For Healthy Living</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>0</v>
@@ -7976,19 +7976,19 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="9" t="n">
-        <v>1</v>
+      <c r="X75" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8006,15 +8006,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>3492833</v>
+        <v>7913211</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Waltair Toastmasters Club</t>
+          <t>Vijayawada Toastmasters Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8055,16 +8055,16 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -8072,20 +8072,20 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="10" t="n">
-        <v>4</v>
+      <c r="V76" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X76" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X76" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="10" t="n">
-        <v>1</v>
+      <c r="Z76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8099,15 +8099,15 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>7657911</v>
+        <v>3492833</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Kiet Toastmasters Club</t>
+          <t>Waltair Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8151,29 +8151,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P77" s="10" t="n">
+      <c r="P77" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q77" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -8200,15 +8200,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>7780796</v>
+        <v>7657911</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>KW's Silver Tongue Toastmasters Club</t>
+          <t>Kiet Toastmasters Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L78" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8248,23 +8248,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P78" s="9" t="n">
-        <v>0</v>
+      <c r="P78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V78" s="9" t="n">
         <v>1</v>
@@ -8273,13 +8273,13 @@
         <v>0</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8297,15 +8297,15 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>7402154</v>
+        <v>7780796</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Pragati Toastmasters Club</t>
+          <t>KW's Silver Tongue Toastmasters Club</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,10 +8319,10 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K79" s="4" t="n">
         <v>1</v>
@@ -8355,10 +8355,10 @@
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T79" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T79" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U79" s="9" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8394,15 +8394,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>7327622</v>
+        <v>7402154</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>S.R.K.R. Toastmasters</t>
+          <t>Pragati Toastmasters Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8452,28 +8452,28 @@
         <v>0</v>
       </c>
       <c r="S80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X80" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8487,19 +8487,19 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>28675850</v>
+        <v>7327622</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>EA Games (India) Toastmasters Club</t>
+          <t>S.R.K.R. Toastmasters</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,17 +8513,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8540,19 +8540,19 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q81" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T81" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
@@ -8564,13 +8564,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="10" t="n">
-        <v>1</v>
+      <c r="Z81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -8588,15 +8588,15 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>28678862</v>
+        <v>28675850</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Espirit Toastmaster Club</t>
+          <t>EA Games (India) Toastmasters Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8610,17 +8610,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -8637,19 +8637,19 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U82" s="9" t="n">
         <v>0</v>
@@ -8660,14 +8660,14 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="9" t="n">
-        <v>1</v>
+      <c r="X82" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>28680398</v>
+        <v>28678862</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>MITS Toastmasters Club</t>
+          <t>Espirit Toastmaster Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -8707,17 +8707,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -8757,8 +8757,8 @@
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="10" t="n">
-        <v>4</v>
+      <c r="X83" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -8782,11 +8782,11 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>28675816</v>
+        <v>28680398</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Sanskrithi Toastmasters Club</t>
+          <t>MITS Toastmasters Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -8804,25 +8804,25 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L84" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O84" s="7" t="inlineStr">
@@ -8854,8 +8854,8 @@
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="9" t="n">
-        <v>0</v>
+      <c r="X84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -8863,8 +8863,8 @@
       <c r="Z84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA84" s="9" t="n">
-        <v>0</v>
+      <c r="AA84" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -8879,15 +8879,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>7893922</v>
+        <v>28675816</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>SRIT - Eloquent Speakers</t>
+          <t>Sanskrithi Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K85" s="4" t="n">
         <v>0</v>
@@ -8915,11 +8915,11 @@
         </is>
       </c>
       <c r="M85" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O85" s="7" t="inlineStr">
@@ -8937,10 +8937,10 @@
         <v>0</v>
       </c>
       <c r="S85" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -8951,8 +8951,8 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="10" t="n">
-        <v>7</v>
+      <c r="X85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
@@ -8960,8 +8960,8 @@
       <c r="Z85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA85" s="10" t="n">
-        <v>1</v>
+      <c r="AA85" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -8976,15 +8976,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7981787</v>
+        <v>7893922</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>SRIT Vibrant Speakers</t>
+          <t>SRIT - Eloquent Speakers</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,10 +8998,10 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K86" s="4" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -9049,13 +9049,13 @@
         <v>0</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9069,19 +9069,19 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>28680110</v>
+        <v>7981787</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Arrise Toastmasters - Hyderabad Chapter</t>
+          <t>SRIT Vibrant Speakers</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,17 +9095,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9125,19 +9125,19 @@
         <v>0</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" s="9" t="n">
-        <v>0</v>
+      <c r="S87" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T87" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V87" s="9" t="n">
         <v>0</v>
@@ -9146,13 +9146,13 @@
         <v>0</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9170,15 +9170,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>28678595</v>
+        <v>28680110</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>BVRIT Narsapur Toastmasters Club</t>
+          <t>Arrise Toastmasters - Hyderabad Chapter</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,17 +9192,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9218,32 +9218,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P88" s="10" t="n">
+      <c r="P88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="Q88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X88" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9267,15 +9267,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>28677199</v>
+        <v>28678595</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>CDK Hyderabad Toastmasters Club</t>
+          <t>BVRIT Narsapur Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9315,8 +9315,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P89" s="9" t="n">
-        <v>0</v>
+      <c r="P89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9340,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9364,15 +9364,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>7995917</v>
+        <v>28677199</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>FactSet India Toastmasters Club</t>
+          <t>CDK Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         <v>0</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9461,11 +9461,11 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>28676879</v>
+        <v>7995917</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Walk the Talk Hyderabad</t>
+          <t>FactSet India Toastmasters Club</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9549,20 +9549,20 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>6692382</v>
+        <v>28676879</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Impact Toastmasters Club</t>
+          <t>Walk the Talk Hyderabad</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>1</v>
@@ -9616,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -9625,13 +9625,13 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>0</v>
+      <c r="X92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -9655,15 +9655,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>7806306</v>
+        <v>6692382</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>InfoBeans Toastmasters Club</t>
+          <t>Impact Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9703,32 +9703,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P93" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q93" s="10" t="n">
+      <c r="P93" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="Q93" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S93" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T93" s="10" t="n">
-        <v>1</v>
+      <c r="S93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X93" s="9" t="n">
-        <v>0</v>
+      <c r="X93" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -9752,15 +9752,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>28678283</v>
+        <v>7806306</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>MPOnline Toastmasters Club</t>
+          <t>InfoBeans Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -9800,32 +9800,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W94" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="X94" s="9" t="n">
-        <v>0</v>
+      <c r="P94" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V94" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>6977979</v>
+        <v>28678283</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>TCS Maitree Toastmasters Club Indore</t>
+          <t>MPOnline Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>19</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -9915,20 +9915,20 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" s="9" t="n">
-        <v>0</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W95" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="X95" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -9942,19 +9942,19 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>28678995</v>
+        <v>6977979</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Bhopal Orators Toastmasters Club</t>
+          <t>TCS Maitree Toastmasters Club Indore</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
@@ -10013,19 +10013,19 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="9" t="n">
-        <v>0</v>
+      <c r="X96" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10043,15 +10043,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>2587096</v>
+        <v>28678995</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Transcendence</t>
+          <t>Bhopal Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10101,28 +10101,28 @@
         <v>0</v>
       </c>
       <c r="S97" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T97" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="10" t="n">
+      <c r="V97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W97" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X97" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="10" t="n">
-        <v>1</v>
+      <c r="Z97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10144,11 +10144,11 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Virtuomasters Club</t>
+          <t>Les orateurs francophones de l'Inde</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10206,20 +10206,20 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X98" s="9" t="n">
-        <v>0</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W98" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10237,15 +10237,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>28679244</v>
+        <v>2587096</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>VIT Bhopal Toastmasters Club</t>
+          <t>Transcendence</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,17 +10259,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10295,28 +10295,28 @@
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X99" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -10330,19 +10330,19 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>7160333</v>
+        <v>28679244</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>HITAM Toastmasters Club</t>
+          <t>VIT Bhopal Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>0</v>
@@ -10391,8 +10391,8 @@
       <c r="R100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="10" t="n">
-        <v>2</v>
+      <c r="S100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T100" s="9" t="n">
         <v>0</v>
@@ -10431,15 +10431,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28676180</v>
+        <v>7160333</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Innobox Toastmasters Club</t>
+          <t>HITAM Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
         <v>0</v>
@@ -10480,17 +10480,17 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="T101" s="9" t="n">
         <v>0</v>
       </c>
@@ -10503,14 +10503,14 @@
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="9" t="n">
-        <v>0</v>
+      <c r="X101" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>4731654</v>
+        <v>28676180</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>JPMC Hyderabad Toastmasters</t>
+          <t>Innobox Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -10595,19 +10595,19 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>0</v>
+      <c r="X102" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="10" t="n">
-        <v>1</v>
+      <c r="Z102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>2254770</v>
+        <v>4731654</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters at Novartis Hyderabad</t>
+          <t>JPMC Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K103" s="4" t="n">
         <v>1</v>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -10697,14 +10697,14 @@
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="9" t="n">
-        <v>0</v>
+      <c r="X103" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28679234</v>
+        <v>2254770</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club @ MEIC</t>
+          <t>Toastmasters at Novartis Hyderabad</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,17 +10744,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-50</v>
-      </c>
-      <c r="L104" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -10789,19 +10789,19 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10815,15 +10815,15 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28680085</v>
+        <v>28679234</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>CBRE D&amp;T Toastmasters Club</t>
+          <t>Toastmasters Club @ MEIC</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -10841,17 +10841,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-50</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -10916,11 +10916,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28677436</v>
+        <v>28680085</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Diebold Nixdorf India Toastmasters Club</t>
+          <t>CBRE D&amp;T Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>0</v>
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="X106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11013,15 +11013,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>7454302</v>
+        <v>28677436</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Dilsukhnagar Toastmasters</t>
+          <t>Diebold Nixdorf India Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11073,26 +11073,26 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="10" t="n">
-        <v>1</v>
+      <c r="T107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="9" t="n">
-        <v>0</v>
+      <c r="X107" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="10" t="n">
-        <v>1</v>
+      <c r="Z107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28680749</v>
+        <v>7454302</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Evernorth Hyderabad Toastmasters</t>
+          <t>Dilsukhnagar Toastmasters</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11170,26 +11170,26 @@
       <c r="S108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>0</v>
+      <c r="X108" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11207,15 +11207,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>1937401</v>
+        <v>28680749</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Golden Falcon Toastmasters</t>
+          <t>Evernorth Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11256,16 +11256,16 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q109" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R109" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11273,14 +11273,14 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="10" t="n">
-        <v>4</v>
+      <c r="V109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X109" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X109" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11304,15 +11304,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28678657</v>
+        <v>1937401</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>LSEG Toast Masters Club - HYD</t>
+          <t>Golden Falcon Toastmasters</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11353,16 +11353,16 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q110" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R110" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" s="9" t="n">
         <v>0</v>
@@ -11370,20 +11370,20 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>0</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="X110" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -11397,15 +11397,15 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>6887490</v>
+        <v>28678657</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Guntur Toastmasters Club</t>
+          <t>LSEG Toast Masters Club - HYD</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K111" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11473,8 +11473,8 @@
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="9" t="n">
-        <v>0</v>
+      <c r="X111" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11498,15 +11498,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>28680227</v>
+        <v>6887490</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Rungta University Ignite Toastmasters Club</t>
+          <t>Guntur Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11564,20 +11564,20 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W112" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="10" t="n">
-        <v>1</v>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11595,15 +11595,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>7185394</v>
+        <v>28680227</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>SSIPMT Spellbinders</t>
+          <t>Rungta University Ignite Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -11661,14 +11661,14 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W113" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X113" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11692,11 +11692,11 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28678601</v>
+        <v>7185394</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>SSIPS Enchanters</t>
+          <t>SSIPMT Spellbinders</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -11714,17 +11714,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L114" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -11764,8 +11764,8 @@
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>0</v>
+      <c r="X114" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -11780,24 +11780,24 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>1466666</v>
+        <v>28678601</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>ADP Hyderabad Toastmasters</t>
+          <t>SSIPS Enchanters</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -11849,26 +11849,26 @@
       <c r="S115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" s="10" t="n">
-        <v>1</v>
+      <c r="T115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="9" t="n">
-        <v>2</v>
+      <c r="X115" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -11886,15 +11886,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28677880</v>
+        <v>1466666</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>AMD Hyderabad Toastmasters Club</t>
+          <t>ADP Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,17 +11908,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -11946,11 +11946,11 @@
       <c r="S116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
+      <c r="T116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V116" s="9" t="n">
         <v>0</v>
@@ -11959,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>7308980</v>
+        <v>28677880</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>ANURAG Toastmasters</t>
+          <t>AMD Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,17 +12005,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12034,8 +12034,8 @@
       <c r="P117" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" s="10" t="n">
-        <v>2</v>
+      <c r="Q117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12049,20 +12049,20 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W117" s="10" t="n">
-        <v>4</v>
+      <c r="V117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>28678783</v>
+        <v>7308980</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Prolifics Toastmasters</t>
+          <t>ANURAG Toastmasters</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,25 +12102,25 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O118" s="7" t="inlineStr">
@@ -12129,16 +12129,16 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q118" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12146,23 +12146,23 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" s="9" t="n">
-        <v>3</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W118" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X118" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA118" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>3123809</v>
+        <v>28678783</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Secunderabad Toastmasters</t>
+          <t>Prolifics Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,67 +12199,67 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M119" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N119" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O119" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA119" s="10" t="n">
-        <v>1</v>
+      <c r="AA119" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>4504233</v>
+        <v>3123809</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>TECH mahindra Toastmasters Club (Infocity)</t>
+          <t>Secunderabad Toastmasters</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -12334,20 +12334,20 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>1</v>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -12367,15 +12367,15 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28677696</v>
+        <v>4504233</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Carrier Hyderabad Toastmasters Club</t>
+          <t>TECH mahindra Toastmasters Club (Infocity)</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12438,13 +12438,13 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12468,11 +12468,11 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1036431</v>
+        <v>28677696</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Deloitte Hyderabad Toastmasters Club</t>
+          <t>Carrier Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>28678481</v>
+        <v>1036431</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>OpenText Hyderabad Toastmasters Club</t>
+          <t>Deloitte Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J123" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="J123" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="K123" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -12614,31 +12614,31 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W123" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28677124</v>
+        <v>28678481</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Vasavi Toastmasters Club</t>
+          <t>OpenText Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -12720,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T124" s="9" t="n">
         <v>0</v>
@@ -12728,14 +12728,14 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>0</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>4637951</v>
+        <v>28677124</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Xlrators-Miyapur</t>
+          <t>Vasavi Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
@@ -12825,14 +12825,14 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="10" t="n">
-        <v>4</v>
+      <c r="V125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12852,19 +12852,19 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7860741</v>
+        <v>4637951</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Carelon Influencers</t>
+          <t>Xlrators-Miyapur</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,17 +12878,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -12905,16 +12905,16 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -12922,20 +12922,20 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>0</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -12953,11 +12953,11 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28680898</v>
+        <v>7860741</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>General Datum Toastmasters Club</t>
+          <t>Carelon Influencers</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -12975,17 +12975,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13025,14 +13025,14 @@
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="9" t="n">
-        <v>0</v>
+      <c r="X127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z127" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>946002</v>
+        <v>28680898</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad Toastmasters</t>
+          <t>General Datum Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13099,37 +13099,37 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q128" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28679268</v>
+        <v>946002</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Quantium India Toastmasters</t>
+          <t>Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,25 +13169,25 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O129" s="7" t="inlineStr">
@@ -13196,10 +13196,10 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q129" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
@@ -13213,23 +13213,23 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="9" t="n">
-        <v>0</v>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X129" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA129" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -13244,11 +13244,11 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28678070</v>
+        <v>28679268</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Thryve Digital Hyderabad Toast Masters</t>
+          <t>Quantium India Toastmasters</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0</v>
@@ -13280,11 +13280,11 @@
         </is>
       </c>
       <c r="M130" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O130" s="7" t="inlineStr">
@@ -13317,7 +13317,7 @@
         <v>0</v>
       </c>
       <c r="X130" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -13325,8 +13325,8 @@
       <c r="Z130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA130" s="10" t="n">
-        <v>1</v>
+      <c r="AA130" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -13341,15 +13341,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>2694327</v>
+        <v>28678070</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters CBIT</t>
+          <t>Thryve Digital Hyderabad Toast Masters</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K131" s="4" t="n">
         <v>0</v>
@@ -13401,11 +13401,11 @@
       <c r="S131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U131" s="10" t="n">
-        <v>1</v>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
         <v>0</v>
@@ -13414,7 +13414,7 @@
         <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13434,15 +13434,15 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28679838</v>
+        <v>2694327</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Amazon HYD Toastmasters Club</t>
+          <t>Toastmasters CBIT</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -13460,17 +13460,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -13487,10 +13487,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -13498,26 +13498,26 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" s="10" t="n">
-        <v>4</v>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="10" t="n">
-        <v>1</v>
+      <c r="Z132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28675603</v>
+        <v>28679838</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Avatar Toastmasters Club</t>
+          <t>Amazon HYD Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13593,10 +13593,10 @@
         <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T133" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -13605,10 +13605,10 @@
         <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -13632,15 +13632,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>1431155</v>
+        <v>28675603</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Broadridge Toastmasters Club</t>
+          <t>Avatar Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
@@ -13690,10 +13690,10 @@
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
@@ -13702,7 +13702,7 @@
         <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>7</v>
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>2097754</v>
+        <v>1431155</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Oracle Hyderabad Toastmasters</t>
+          <t>Broadridge Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -13795,20 +13795,20 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>2</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X135" s="9" t="n">
-        <v>1</v>
+      <c r="X135" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28677983</v>
+        <v>28680944</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>ValueMomentum-Hyderabad</t>
+          <t>GE Vernova HTC Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,25 +13848,25 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L136" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O136" s="7" t="inlineStr">
@@ -13904,11 +13904,11 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA136" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -13923,11 +13923,11 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28679192</v>
+        <v>2097754</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Zelis Toastmasters Club</t>
+          <t>Oracle Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -13971,45 +13971,239 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P137" s="10" t="n">
+      <c r="P137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>28677983</v>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>ValueMomentum-Hyderabad</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M138" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>28679192</v>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Zelis Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J139" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M139" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P139" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Q137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA137" s="10" t="n">
+      <c r="Y139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA139" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA137"/>
+  <autoFilter ref="A1:AA139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14096,7 +14290,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14129,7 +14323,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14294,7 +14488,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14327,7 +14521,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14393,7 +14587,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14426,7 +14620,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14459,7 +14653,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.83</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14525,7 +14719,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14555,16 +14749,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -14573,7 +14767,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -14624,7 +14818,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14657,7 +14851,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14690,7 +14884,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14723,7 +14917,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14756,7 +14950,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -14789,7 +14983,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14804,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -14822,7 +15016,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14855,7 +15049,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14987,7 +15181,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -15017,25 +15211,25 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
         <v>6</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1044,17 +1044,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1141,17 +1141,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1179,8 +1179,8 @@
       <c r="S5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T5" s="9" t="n">
-        <v>0</v>
+      <c r="T5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U5" s="9" t="n">
         <v>0</v>
@@ -1238,17 +1238,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1529,17 +1529,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,17 +1820,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1858,8 +1858,8 @@
       <c r="S12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -2014,17 +2014,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>65</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-65</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2111,17 +2111,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-31</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-57</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" s="9" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2596,17 +2596,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3804,8 +3804,8 @@
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>0</v>
+      <c r="V32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -3998,8 +3998,8 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>2</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4095,8 +4095,8 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>2</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4148,17 +4148,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4245,17 +4245,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -4774,11 +4774,11 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="9" t="n">
-        <v>0</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W42" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>7</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -4871,8 +4871,8 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>3</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5356,11 +5356,11 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>0</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5841,11 +5841,11 @@
       <c r="U53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>2</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="9" t="n">
         <v>2</v>
@@ -5894,17 +5894,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6035,11 +6035,11 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" s="9" t="n">
-        <v>0</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>5</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -6185,17 +6185,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-26</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6408,8 +6408,8 @@
       <c r="P59" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q59" s="9" t="n">
-        <v>1</v>
+      <c r="Q59" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>1</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6617,11 +6617,11 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="9" t="n">
-        <v>0</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W61" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X61" s="9" t="n">
         <v>1</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,17 +6670,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -6714,11 +6714,11 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="9" t="n">
-        <v>0</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>4</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6811,11 +6811,11 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="9" t="n">
-        <v>0</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W63" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>6</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7199,8 +7199,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,17 +7252,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>5</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7587,8 +7587,8 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>0</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8125,17 +8125,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8266,11 +8266,11 @@
       <c r="U78" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>1</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>7</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -8654,11 +8654,11 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>0</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>6</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>22</v>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9042,11 +9042,11 @@
       <c r="U86" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" s="9" t="n">
-        <v>0</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W86" s="10" t="n">
+        <v>21</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,17 +9095,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>18</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9139,11 +9139,11 @@
       <c r="U87" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" s="9" t="n">
-        <v>0</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W87" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>5</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9333,11 +9333,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>0</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9430,11 +9430,11 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>0</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>5</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9624,11 +9624,11 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>1</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>4</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9721,11 +9721,11 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
+      <c r="V93" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W93" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W93" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -9774,17 +9774,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10210,7 +10210,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>4</v>
@@ -10259,17 +10259,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10307,7 +10307,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>7</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,17 +10453,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10497,11 +10497,11 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="9" t="n">
-        <v>0</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W101" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>5</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-39</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10744,17 +10744,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -10938,17 +10938,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11035,17 +11035,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11168,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" s="10" t="n">
         <v>1</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11285,8 +11285,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11373,8 +11373,8 @@
       <c r="V110" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W110" s="9" t="n">
-        <v>3</v>
+      <c r="W110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11908,17 +11908,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-27</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>8</v>
+        <v>-6</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>2</v>
       </c>
       <c r="R118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S118" s="9" t="n">
         <v>1</v>
@@ -12150,7 +12150,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>7</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -12534,11 +12534,11 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" s="9" t="n">
-        <v>0</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W122" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>7</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -12631,8 +12631,8 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>3</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -12731,8 +12731,8 @@
       <c r="V124" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W124" s="9" t="n">
-        <v>3</v>
+      <c r="W124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>6</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12925,8 +12925,8 @@
       <c r="V126" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W126" s="9" t="n">
-        <v>3</v>
+      <c r="W126" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>5</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>9</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>6</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -13993,7 +13993,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>4</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -14183,11 +14183,11 @@
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W139" s="9" t="n">
-        <v>0</v>
+      <c r="V139" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W139" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X139" s="10" t="n">
         <v>6</v>
@@ -14290,7 +14290,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14305,7 +14305,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -14338,7 +14338,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -14356,7 +14356,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14371,7 +14371,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -14404,7 +14404,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14437,7 +14437,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -14503,7 +14503,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -14521,7 +14521,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -14587,7 +14587,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14602,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -14620,7 +14620,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14686,7 +14686,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -14701,7 +14701,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -14719,13 +14719,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -14734,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -14752,7 +14752,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14767,7 +14767,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -14785,7 +14785,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14833,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14851,13 +14851,13 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -14884,13 +14884,13 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.83</v>
+        <v>2.83</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -14899,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -14917,7 +14917,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14932,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -14950,7 +14950,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -15016,7 +15016,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15031,7 +15031,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -15049,13 +15049,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -15064,7 +15064,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -15130,7 +15130,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -15148,7 +15148,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -15163,7 +15163,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -15214,7 +15214,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA139"/>
+  <dimension ref="A1:AA140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1820,17 +1820,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2537,8 +2537,8 @@
       <c r="S19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="9" t="n">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5350,8 +5350,8 @@
       <c r="S48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T48" s="9" t="n">
-        <v>0</v>
+      <c r="T48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U48" s="9" t="n">
         <v>0</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6185,17 +6185,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-26</v>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6229,11 +6229,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W57" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>6</v>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q59" s="10" t="n">
         <v>2</v>
@@ -6573,17 +6573,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6621,7 +6621,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X61" s="9" t="n">
         <v>1</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7279,16 +7279,16 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="9" t="n">
-        <v>0</v>
+      <c r="S68" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>1</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -7909,11 +7909,11 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>28676684</v>
+        <v>28681033</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Sattvic Toastmasters For Healthy Living</t>
+          <t>IIAM Vizag Toastmasters</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -7931,17 +7931,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -7976,19 +7976,19 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="W75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8006,15 +8006,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>7913211</v>
+        <v>28676684</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Vijayawada Toastmasters Club</t>
+          <t>Sattvic Toastmasters For Healthy Living</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8073,19 +8073,19 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X76" s="9" t="n">
-        <v>1</v>
+      <c r="X76" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8103,15 +8103,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>3492833</v>
+        <v>7913211</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Waltair Toastmasters Club</t>
+          <t>Vijayawada Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8152,16 +8152,16 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q77" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T77" s="9" t="n">
         <v>0</v>
@@ -8169,20 +8169,20 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="10" t="n">
-        <v>4</v>
+      <c r="V77" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X77" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X77" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="10" t="n">
-        <v>1</v>
+      <c r="Z77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8196,19 +8196,19 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>7657911</v>
+        <v>3492833</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Kiet Toastmasters Club</t>
+          <t>Waltair Toastmasters Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8248,23 +8248,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P78" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q78" s="9" t="n">
-        <v>1</v>
+      <c r="P78" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q78" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" s="10" t="n">
-        <v>1</v>
+      <c r="S78" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V78" s="10" t="n">
         <v>4</v>
@@ -8297,15 +8297,15 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>7780796</v>
+        <v>7657911</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>KW's Silver Tongue Toastmasters Club</t>
+          <t>Kiet Toastmasters Club</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L79" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8345,32 +8345,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P79" s="9" t="n">
-        <v>0</v>
+      <c r="P79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8394,15 +8394,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>7402154</v>
+        <v>7780796</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Pragati Toastmasters Club</t>
+          <t>KW's Silver Tongue Toastmasters Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8452,22 +8452,22 @@
         <v>0</v>
       </c>
       <c r="S80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T80" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X80" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8491,15 +8491,15 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>7327622</v>
+        <v>7402154</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>S.R.K.R. Toastmasters</t>
+          <t>Pragati Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8549,28 +8549,28 @@
         <v>0</v>
       </c>
       <c r="S81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -8584,19 +8584,19 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>28675850</v>
+        <v>7327622</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>EA Games (India) Toastmasters Club</t>
+          <t>S.R.K.R. Toastmasters</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8610,17 +8610,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>-9</v>
       </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -8637,37 +8637,37 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T82" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="10" t="n">
+      <c r="V82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W82" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X82" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="10" t="n">
-        <v>1</v>
+      <c r="Z82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8685,15 +8685,15 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>28678862</v>
+        <v>28675850</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Espirit Toastmaster Club</t>
+          <t>EA Games (India) Toastmasters Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,17 +8707,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -8734,37 +8734,37 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q83" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>0</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X83" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -8782,15 +8782,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>28680398</v>
+        <v>28678862</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>MITS Toastmasters Club</t>
+          <t>Espirit Toastmaster Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8804,17 +8804,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -8854,14 +8854,14 @@
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="10" t="n">
-        <v>4</v>
+      <c r="X84" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="10" t="n">
-        <v>1</v>
+      <c r="Z84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -8879,15 +8879,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>28675816</v>
+        <v>28680398</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Sanskrithi Toastmasters Club</t>
+          <t>MITS Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,25 +8901,25 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K85" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O85" s="7" t="inlineStr">
@@ -8951,17 +8951,17 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="9" t="n">
-        <v>0</v>
+      <c r="X85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -8976,15 +8976,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7893922</v>
+        <v>28675816</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>SRIT - Eloquent Speakers</t>
+          <t>Sanskrithi Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9012,11 +9012,11 @@
         </is>
       </c>
       <c r="M86" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O86" s="7" t="inlineStr">
@@ -9033,32 +9033,32 @@
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U86" s="10" t="n">
-        <v>2</v>
+      <c r="S86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W86" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="X86" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="X86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA86" s="10" t="n">
-        <v>1</v>
+      <c r="Z86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -9073,11 +9073,11 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>7981787</v>
+        <v>7893922</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>SRIT Vibrant Speakers</t>
+          <t>SRIT - Eloquent Speakers</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
@@ -9143,10 +9143,10 @@
         <v>4</v>
       </c>
       <c r="W87" s="10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9166,19 +9166,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>28680110</v>
+        <v>7981787</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Arrise Toastmasters - Hyderabad Chapter</t>
+          <t>SRIT Vibrant Speakers</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9222,34 +9222,34 @@
         <v>0</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" s="9" t="n">
-        <v>0</v>
+      <c r="S88" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V88" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W88" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="X88" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9267,15 +9267,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>28678595</v>
+        <v>28680110</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>BVRIT Narsapur Toastmasters Club</t>
+          <t>Arrise Toastmasters - Hyderabad Chapter</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9315,38 +9315,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P89" s="10" t="n">
+      <c r="P89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W89" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X89" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="10" t="n">
-        <v>1</v>
+      <c r="Z89" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -9364,15 +9364,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>28677199</v>
+        <v>28678595</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>CDK Hyderabad Toastmasters Club</t>
+          <t>BVRIT Narsapur Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9412,8 +9412,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P90" s="9" t="n">
-        <v>0</v>
+      <c r="P90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       <c r="V90" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W90" s="9" t="n">
-        <v>1</v>
+      <c r="W90" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -9461,15 +9461,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>7995917</v>
+        <v>28677199</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>FactSet India Toastmasters Club</t>
+          <t>CDK Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9486,10 +9486,10 @@
         <v>20</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -9527,14 +9527,14 @@
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="9" t="n">
-        <v>0</v>
+      <c r="V91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -9558,15 +9558,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>28676879</v>
+        <v>7995917</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Walk the Talk Hyderabad</t>
+          <t>FactSet India Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9610,7 +9610,7 @@
         <v>1</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -9624,11 +9624,11 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="10" t="n">
-        <v>4</v>
+      <c r="V92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>4</v>
@@ -9646,20 +9646,20 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>6692382</v>
+        <v>28676879</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Impact Toastmasters Club</t>
+          <t>Walk the Talk Hyderabad</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -9677,17 +9677,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -9713,7 +9713,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -9725,10 +9725,10 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -9752,15 +9752,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>7806306</v>
+        <v>6692382</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>InfoBeans Toastmasters Club</t>
+          <t>Impact Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,17 +9774,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -9800,29 +9800,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P94" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q94" s="10" t="n">
+      <c r="P94" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R94" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S94" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T94" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U94" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V94" s="9" t="n">
-        <v>2</v>
+      <c r="Q94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>7</v>
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>28678283</v>
+        <v>7806306</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>MPOnline Toastmasters Club</t>
+          <t>InfoBeans Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9897,32 +9897,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" s="9" t="n">
-        <v>0</v>
+      <c r="P95" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q95" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R95" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S95" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V95" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W95" s="10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -9946,15 +9946,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>6977979</v>
+        <v>28678283</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>TCS Maitree Toastmasters Club Indore</t>
+          <t>MPOnline Toastmasters Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,17 +9968,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L96" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
@@ -10012,14 +10012,14 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W96" s="9" t="n">
-        <v>0</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W96" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="X96" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10039,19 +10039,19 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>28678995</v>
+        <v>6977979</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Bhopal Orators Toastmasters Club</t>
+          <t>TCS Maitree Toastmasters Club Indore</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10140,15 +10140,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>7778934</v>
+        <v>28678995</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Les orateurs francophones de l'Inde</t>
+          <t>Bhopal Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10206,11 +10206,11 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W98" s="10" t="n">
-        <v>6</v>
+      <c r="V98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>4</v>
@@ -10218,8 +10218,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="10" t="n">
-        <v>1</v>
+      <c r="Z98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10237,15 +10237,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>2587096</v>
+        <v>7778934</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Transcendence</t>
+          <t>Les orateurs francophones de l'Inde</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10295,22 +10295,22 @@
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T99" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U99" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V99" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W99" s="9" t="n">
-        <v>3</v>
+      <c r="W99" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10334,15 +10334,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>28679244</v>
+        <v>2587096</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>VIT Bhopal Toastmasters Club</t>
+          <t>Transcendence</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10392,28 +10392,28 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W100" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X100" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -10427,19 +10427,19 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>7160333</v>
+        <v>28679244</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>HITAM Toastmasters Club</t>
+          <t>VIT Bhopal Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,17 +10453,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10488,8 +10488,8 @@
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S101" s="10" t="n">
-        <v>2</v>
+      <c r="S101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T101" s="9" t="n">
         <v>0</v>
@@ -10497,20 +10497,20 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W101" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="X101" s="10" t="n">
-        <v>5</v>
+      <c r="V101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="10" t="n">
-        <v>1</v>
+      <c r="Z101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28676180</v>
+        <v>7160333</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Innobox Toastmasters Club</t>
+          <t>HITAM Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L102" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -10577,37 +10577,37 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="T102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="9" t="n">
-        <v>0</v>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W102" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>4731654</v>
+        <v>28676180</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>JPMC Hyderabad Toastmasters</t>
+          <t>Innobox Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-39</v>
+        <v>-13</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -10703,8 +10703,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="10" t="n">
-        <v>1</v>
+      <c r="Z103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10722,11 +10722,11 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2254770</v>
+        <v>4731654</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters at Novartis Hyderabad</t>
+          <t>JPMC Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-16</v>
+        <v>-39</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -10794,8 +10794,8 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>2</v>
+      <c r="X104" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -10819,15 +10819,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28679234</v>
+        <v>2254770</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club @ MEIC</t>
+          <t>Toastmasters at Novartis Hyderabad</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-50</v>
+        <v>-16</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -10886,19 +10886,19 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -10912,15 +10912,15 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28680085</v>
+        <v>28679234</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>CBRE D&amp;T Toastmasters Club</t>
+          <t>Toastmasters Club @ MEIC</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -10941,10 +10941,10 @@
         <v>0</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="X106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11013,11 +11013,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28677436</v>
+        <v>28680085</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Diebold Nixdorf India Toastmasters Club</t>
+          <t>CBRE D&amp;T Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11038,10 +11038,10 @@
         <v>0</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11085,8 +11085,8 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="10" t="n">
-        <v>7</v>
+      <c r="X107" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>7454302</v>
+        <v>28677436</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Dilsukhnagar Toastmasters</t>
+          <t>Diebold Nixdorf India Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-7</v>
+        <v>-24</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11168,16 +11168,16 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11188,8 +11188,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="10" t="n">
-        <v>1</v>
+      <c r="Z108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11207,15 +11207,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28680749</v>
+        <v>7454302</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Evernorth Hyderabad Toastmasters</t>
+          <t>Dilsukhnagar Toastmasters</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,17 +11229,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11265,16 +11265,16 @@
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11304,15 +11304,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1937401</v>
+        <v>28680749</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Golden Falcon Toastmasters</t>
+          <t>Evernorth Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11353,16 +11353,16 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q110" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R110" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T110" s="9" t="n">
         <v>0</v>
@@ -11370,11 +11370,11 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W110" s="10" t="n">
-        <v>4</v>
+      <c r="V110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -11401,15 +11401,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28678657</v>
+        <v>1937401</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>LSEG Toast Masters Club - HYD</t>
+          <t>Golden Falcon Toastmasters</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-12</v>
+        <v>5</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11450,16 +11450,16 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q111" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R111" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T111" s="9" t="n">
         <v>0</v>
@@ -11467,14 +11467,14 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11494,19 +11494,19 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>6887490</v>
+        <v>28678657</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Guntur Toastmasters Club</t>
+          <t>LSEG Toast Masters Club - HYD</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11565,19 +11565,19 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11595,15 +11595,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28680227</v>
+        <v>6887490</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Rungta University Ignite Toastmasters Club</t>
+          <t>Guntur Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,17 +11617,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -11653,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -11661,11 +11661,11 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W113" s="10" t="n">
-        <v>4</v>
+      <c r="V113" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>7</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="10" t="n">
-        <v>1</v>
+      <c r="Z113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>7185394</v>
+        <v>28680227</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>SSIPMT Spellbinders</t>
+          <t>Rungta University Ignite Toastmasters Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-11</v>
+        <v>8</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" s="9" t="n">
         <v>0</v>
@@ -11758,11 +11758,11 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W114" s="9" t="n">
-        <v>0</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>7</v>
@@ -11789,11 +11789,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>28678601</v>
+        <v>7185394</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>SSIPS Enchanters</t>
+          <t>SSIPMT Spellbinders</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L115" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -11877,24 +11877,24 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1466666</v>
+        <v>28678601</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>ADP Hyderabad Toastmasters</t>
+          <t>SSIPS Enchanters</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-27</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11946,26 +11946,26 @@
       <c r="S116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" s="10" t="n">
-        <v>1</v>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>28677880</v>
+        <v>1466666</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>AMD Hyderabad Toastmasters Club</t>
+          <t>ADP Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-2</v>
+        <v>-27</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -12043,11 +12043,11 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V117" s="9" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>7308980</v>
+        <v>28677880</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>ANURAG Toastmasters</t>
+          <t>AMD Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12131,14 +12131,14 @@
       <c r="P118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" s="10" t="n">
-        <v>2</v>
+      <c r="Q118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12146,20 +12146,20 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W118" s="10" t="n">
-        <v>6</v>
+      <c r="V118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="10" t="n">
-        <v>1</v>
+      <c r="Z118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28678783</v>
+        <v>7308980</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Prolifics Toastmasters</t>
+          <t>ANURAG Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,25 +12199,25 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O119" s="7" t="inlineStr">
@@ -12226,16 +12226,16 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" s="9" t="n">
         <v>0</v>
@@ -12243,14 +12243,14 @@
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W119" s="9" t="n">
-        <v>0</v>
+      <c r="V119" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W119" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12258,8 +12258,8 @@
       <c r="Z119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA119" s="9" t="n">
-        <v>0</v>
+      <c r="AA119" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>3123809</v>
+        <v>28678783</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Secunderabad Toastmasters</t>
+          <t>Prolifics Toastmasters</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,25 +12296,25 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O120" s="7" t="inlineStr">
@@ -12334,29 +12334,29 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="10" t="n">
-        <v>1</v>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="10" t="n">
+      <c r="V120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA120" s="10" t="n">
-        <v>1</v>
+      <c r="AA120" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>4504233</v>
+        <v>3123809</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>TECH mahindra Toastmasters Club (Infocity)</t>
+          <t>Secunderabad Toastmasters</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12431,20 +12431,20 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>1</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12464,19 +12464,19 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28677696</v>
+        <v>4504233</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Carrier Hyderabad Toastmasters Club</t>
+          <t>TECH mahindra Toastmasters Club (Infocity)</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -12534,14 +12534,14 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W122" s="10" t="n">
+      <c r="V122" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="10" t="n">
         <v>6</v>
-      </c>
-      <c r="X122" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1036431</v>
+        <v>28677696</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Deloitte Hyderabad Toastmasters Club</t>
+          <t>Carrier Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -12634,8 +12634,8 @@
       <c r="V123" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
+      <c r="W123" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>7</v>
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28678481</v>
+        <v>1036431</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>OpenText Hyderabad Toastmasters Club</t>
+          <t>Deloitte Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -12731,11 +12731,11 @@
       <c r="V124" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W124" s="10" t="n">
-        <v>4</v>
+      <c r="W124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28677124</v>
+        <v>28678481</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Vasavi Toastmasters Club</t>
+          <t>OpenText Hyderabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -12817,7 +12817,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -12825,14 +12825,14 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>4637951</v>
+        <v>28677124</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Xlrators-Miyapur</t>
+          <t>Vasavi Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,17 +12878,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -12908,7 +12908,7 @@
         <v>1</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -12922,14 +12922,14 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W126" s="10" t="n">
-        <v>5</v>
+      <c r="V126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -12949,19 +12949,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>7860741</v>
+        <v>4637951</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Carelon Influencers</t>
+          <t>Xlrators-Miyapur</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,17 +12975,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13002,16 +13002,16 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" s="9" t="n">
         <v>0</v>
@@ -13019,14 +13019,14 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W127" s="9" t="n">
-        <v>0</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W127" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13050,11 +13050,11 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28680898</v>
+        <v>7860741</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>General Datum Toastmasters Club</t>
+          <t>Carelon Influencers</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13117,19 +13117,19 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="9" t="n">
-        <v>0</v>
+      <c r="X128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z128" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>946002</v>
+        <v>28680898</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad Toastmasters</t>
+          <t>General Datum Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13196,37 +13196,37 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="R129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28679268</v>
+        <v>946002</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Quantium India Toastmasters</t>
+          <t>Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,25 +13266,25 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O130" s="7" t="inlineStr">
@@ -13292,11 +13292,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" s="9" t="n">
-        <v>0</v>
+      <c r="P130" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q130" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -13310,23 +13310,23 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>0</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X130" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA130" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -13341,11 +13341,11 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28678070</v>
+        <v>28679268</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Thryve Digital Hyderabad Toast Masters</t>
+          <t>Quantium India Toastmasters</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13366,10 +13366,10 @@
         <v>0</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13377,11 +13377,11 @@
         </is>
       </c>
       <c r="M131" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O131" s="7" t="inlineStr">
@@ -13413,8 +13413,8 @@
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="10" t="n">
-        <v>4</v>
+      <c r="X131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13422,8 +13422,8 @@
       <c r="Z131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA131" s="10" t="n">
-        <v>1</v>
+      <c r="AA131" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -13438,15 +13438,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>2694327</v>
+        <v>28678070</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters CBIT</t>
+          <t>Thryve Digital Hyderabad Toast Masters</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13487,10 +13487,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -13498,20 +13498,20 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U132" s="10" t="n">
-        <v>9</v>
+      <c r="T132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -13531,15 +13531,15 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28679838</v>
+        <v>2694327</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Amazon HYD Toastmasters Club</t>
+          <t>Toastmasters CBIT</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -13557,17 +13557,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13595,26 +13595,26 @@
       <c r="S133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="10" t="n">
-        <v>4</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V133" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="10" t="n">
-        <v>1</v>
+      <c r="Z133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13632,15 +13632,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28675603</v>
+        <v>28679838</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Avatar Toastmasters Club</t>
+          <t>Amazon HYD Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -13690,10 +13690,10 @@
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T134" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
@@ -13702,10 +13702,10 @@
         <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>1431155</v>
+        <v>28675603</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Broadridge Toastmasters Club</t>
+          <t>Avatar Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -13787,10 +13787,10 @@
         <v>0</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
@@ -13799,7 +13799,7 @@
         <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>7</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28680944</v>
+        <v>1431155</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>GE Vernova HTC Toastmasters Club</t>
+          <t>Broadridge Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
@@ -13892,14 +13892,14 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>1</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="9" t="n">
-        <v>0</v>
+      <c r="X136" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>2097754</v>
+        <v>28680944</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Oracle Hyderabad Toastmasters</t>
+          <t>GE Vernova HTC Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -13989,14 +13989,14 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="10" t="n">
-        <v>4</v>
+      <c r="V137" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X137" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28677983</v>
+        <v>2097754</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>ValueMomentum-Hyderabad</t>
+          <t>Oracle Hyderabad Toastmasters</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,25 +14042,25 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L138" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O138" s="7" t="inlineStr">
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
@@ -14086,23 +14086,23 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>0</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -14117,93 +14117,190 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
+        <v>28677983</v>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>ValueMomentum-Hyderabad</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M139" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
         <v>28679192</v>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>Zelis Toastmasters Club</t>
         </is>
       </c>
-      <c r="E139" s="5" t="n">
+      <c r="E140" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F139" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G139" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
+      <c r="F140" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I139" s="4" t="n">
+      <c r="I140" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="J139" s="4" t="n">
+      <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K139" s="4" t="n">
+      <c r="K140" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L139" s="4" t="inlineStr">
+      <c r="L140" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M139" s="8" t="n">
+      <c r="M140" s="8" t="n">
         <v>46446</v>
       </c>
-      <c r="N139" s="4" t="inlineStr">
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O139" s="7" t="inlineStr">
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P139" s="10" t="n">
+      <c r="P140" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" s="10" t="n">
+      <c r="Q140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W139" s="10" t="n">
+      <c r="W140" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="X139" s="10" t="n">
+      <c r="X140" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Y139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA139" s="10" t="n">
+      <c r="Y140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA140" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA139"/>
+  <autoFilter ref="A1:AA140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14371,7 +14468,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -14422,7 +14519,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -14620,7 +14717,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14686,7 +14783,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -14701,7 +14798,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -14734,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -14752,7 +14849,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14815,16 +14912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -14833,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -14884,7 +14981,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -14899,7 +14996,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -14917,7 +15014,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14932,7 +15029,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -14950,7 +15047,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -14965,7 +15062,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -14983,13 +15080,13 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -15049,7 +15146,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -15181,7 +15278,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/225/inyear.xlsx
+++ b/docs/d/225/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>7</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4759,8 +4759,8 @@
       <c r="P42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>1</v>
+      <c r="Q42" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -4771,8 +4771,8 @@
       <c r="T42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U42" s="9" t="n">
-        <v>0</v>
+      <c r="U42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V42" s="10" t="n">
         <v>4</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>4</v>
       </c>
       <c r="W47" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>7</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5938,8 +5938,8 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>3</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>6</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6405,8 +6405,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P59" s="9" t="n">
-        <v>3</v>
+      <c r="P59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q59" s="10" t="n">
         <v>2</v>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7296,8 +7296,8 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>3</v>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7775,8 +7775,8 @@
       <c r="S73" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7878,8 +7878,8 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>3</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8248,8 +8248,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P78" s="9" t="n">
-        <v>3</v>
+      <c r="P78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q78" s="10" t="n">
         <v>2</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q83" s="10" t="n">
         <v>2</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9800,8 +9800,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P94" s="9" t="n">
-        <v>2</v>
+      <c r="P94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10103,8 +10103,8 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11176,11 +11176,11 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>0</v>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11564,11 +11564,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W112" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>6</v>
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12784,10 +12784,10 @@
         <v>17</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>9</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14684,13 +14684,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -14849,7 +14849,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14882,7 +14882,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14915,13 +14915,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -15047,7 +15047,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -15146,7 +15146,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -15161,7 +15161,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
